--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260618.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>250,894,645</t>
+          <t>2,206,196</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,206,196</t>
+          <t>250,894,645</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>16,186,000</t>
+          <t>64,093,893</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>64,093,893</t>
+          <t>16,186,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,705,000</t>
+          <t>1,210,990</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,210,990</t>
+          <t>1,705,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>104,883,286</t>
+          <t>3,795,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,795,000</t>
+          <t>104,883,286</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>24,141</t>
+          <t>8,051</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>8,051</t>
+          <t>102,294</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>102,294</t>
+          <t>271,957</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>271,957</t>
+          <t>24,141</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
